--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:45</t>
+    <t xml:space="preserve">2026-09-09 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:32</t>
+    <t xml:space="preserve">2026-09-12 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:48</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:26</t>
+    <t xml:space="preserve">2026-09-27 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.04</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="3">
@@ -588,7 +588,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.32</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.92</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.84</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="6">
@@ -639,7 +639,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.78</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.64</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.58</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9">
@@ -690,7 +690,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.39</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="10">
@@ -707,7 +707,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.27</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -724,7 +724,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.17</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.26</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +758,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.27</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="14">
@@ -775,7 +775,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.28</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="15">
@@ -792,7 +792,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.29</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="16">
@@ -809,7 +809,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.32</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="17">
@@ -826,7 +826,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.41</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.41</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +860,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.48</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="20">
@@ -877,7 +877,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.51</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +894,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.63</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.69</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="23">
@@ -928,7 +928,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.75</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="24">
@@ -945,7 +945,7 @@
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.77</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="25">
@@ -962,7 +962,7 @@
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.82</v>
+        <v>-8.2</v>
       </c>
     </row>
     <row r="26">
@@ -979,7 +979,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.93</v>
+        <v>-9.26</v>
       </c>
     </row>
     <row r="27">
@@ -996,7 +996,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.97</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="28">
@@ -1013,7 +1013,7 @@
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-1.01</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="29">
@@ -1030,7 +1030,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-1.36</v>
+        <v>-13.63</v>
       </c>
     </row>
     <row r="30">
@@ -1047,7 +1047,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-1.39</v>
+        <v>-13.89</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1.73</v>
+        <v>-17.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-10-01 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:55</t>
+    <t xml:space="preserve">2026-10-02 13:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:28</t>
+    <t xml:space="preserve">2026-10-05 08:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
